--- a/data_paper_and_repo_publication/manuscript_outputs/census-9_families.xlsx
+++ b/data_paper_and_repo_publication/manuscript_outputs/census-9_families.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/medinaja/GDrive_Science/STRI/STEM_TABLES_FORESTGEO/3_BCI/BCI50ha_StemReconstruction_Rtables/data_paper_and_repo_publication/manuscript_outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6C4AE64-2C73-5644-A35C-45035943D86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A856CB7B-2693-C342-A08C-5A7E583CD146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8D5E41EF-FAA3-7D4F-B356-DFA4D02D52B0}"/>
+    <workbookView xWindow="14060" yWindow="660" windowWidth="14680" windowHeight="18980" xr2:uid="{8D5E41EF-FAA3-7D4F-B356-DFA4D02D52B0}"/>
   </bookViews>
   <sheets>
     <sheet name="census-9_families" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'census-9_families'!$A$1:$G$60</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1704,94 +1720,94 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="E28">
-        <v>0.607289494892988</v>
+        <v>1.37725536977785</v>
       </c>
       <c r="F28">
         <v>0.6</v>
       </c>
       <c r="G28">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>1223</v>
+        <v>1228</v>
       </c>
       <c r="E29">
-        <v>1.37725536977785</v>
+        <v>0.607289494892988</v>
       </c>
       <c r="F29">
         <v>0.6</v>
       </c>
       <c r="G29">
-        <v>0.09</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30">
         <v>1</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="E30">
-        <v>4.3863694173602603</v>
+        <v>41.065037774078498</v>
       </c>
       <c r="F30">
         <v>0.55000000000000004</v>
       </c>
       <c r="G30">
-        <v>0.28000000000000003</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B31">
         <v>1</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>1114</v>
+        <v>1126</v>
       </c>
       <c r="E31">
-        <v>41.065037774078498</v>
+        <v>4.3863694173602603</v>
       </c>
       <c r="F31">
         <v>0.55000000000000004</v>
       </c>
       <c r="G31">
-        <v>2.62</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -2095,48 +2111,48 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>145</v>
       </c>
       <c r="E45">
-        <v>0.63218661667269005</v>
+        <v>11.566870555425099</v>
       </c>
       <c r="F45">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G45">
-        <v>0.04</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>145</v>
       </c>
       <c r="E46">
-        <v>11.566870555425099</v>
+        <v>0.63218661667269005</v>
       </c>
       <c r="F46">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G46">
-        <v>0.74</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
@@ -2187,99 +2203,99 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49">
+        <v>2</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
         <v>54</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
-      </c>
-      <c r="D49">
-        <v>70</v>
-      </c>
       <c r="E49">
-        <v>0.79511903646581805</v>
+        <v>3.3938656852657099</v>
       </c>
       <c r="F49">
         <v>0.03</v>
       </c>
       <c r="G49">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E50">
-        <v>9.5125069356208694E-2</v>
+        <v>0.79511903646581805</v>
       </c>
       <c r="F50">
         <v>0.03</v>
       </c>
       <c r="G50">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
         <v>56</v>
       </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51">
-        <v>54</v>
-      </c>
       <c r="E51">
-        <v>3.3938656852657099</v>
+        <v>9.5125069356208694E-2</v>
       </c>
       <c r="F51">
         <v>0.03</v>
       </c>
       <c r="G51">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E52">
-        <v>9.0949892719587894E-2</v>
+        <v>1.9331256323113699</v>
       </c>
       <c r="F52">
         <v>0.02</v>
       </c>
       <c r="G52">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -2288,39 +2304,39 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E53">
-        <v>1.9331256323113699</v>
+        <v>1.17175201333408</v>
       </c>
       <c r="F53">
         <v>0.02</v>
       </c>
       <c r="G53">
-        <v>0.12</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E54">
-        <v>1.17175201333408</v>
+        <v>9.0949892719587894E-2</v>
       </c>
       <c r="F54">
         <v>0.02</v>
       </c>
       <c r="G54">
-        <v>7.0000000000000007E-2</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
@@ -2462,6 +2478,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G60" xr:uid="{F3AF11B8-8919-9645-A700-F7B7665218B9}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G60">
+      <sortCondition descending="1" ref="F1:F60"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>